--- a/public/exports-from-60/19438414.xlsx
+++ b/public/exports-from-60/19438414.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024938</t>
+          <t xml:space="preserve">310024939</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -24739,7 +24739,7 @@
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t xml:space="preserve">311304440</t>
+          <t xml:space="preserve">311304591</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">

--- a/public/exports-from-60/19438414.xlsx
+++ b/public/exports-from-60/19438414.xlsx
@@ -5989,7 +5989,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024938</t>
+          <t xml:space="preserve">310024942</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024938</t>
+          <t xml:space="preserve">310024942</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024939</t>
+          <t xml:space="preserve">310024942</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024938</t>
+          <t xml:space="preserve">310024942</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024938</t>
+          <t xml:space="preserve">310024942</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6364,7 +6364,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024938</t>
+          <t xml:space="preserve">310024942</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024938</t>
+          <t xml:space="preserve">310024942</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024938</t>
+          <t xml:space="preserve">310024942</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024938</t>
+          <t xml:space="preserve">310024942</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -7339,7 +7339,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311123772</t>
+          <t xml:space="preserve">311123773</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311123772</t>
+          <t xml:space="preserve">311123773</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -9829,12 +9829,12 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -9904,12 +9904,12 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -9979,12 +9979,12 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -10054,12 +10054,12 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -10129,12 +10129,12 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -10204,12 +10204,12 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -10279,12 +10279,12 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -10354,12 +10354,12 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -10429,12 +10429,12 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -10504,12 +10504,12 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -10579,12 +10579,12 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -10654,12 +10654,12 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -10729,12 +10729,12 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -10804,12 +10804,12 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -10879,12 +10879,12 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -10954,12 +10954,12 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -11029,12 +11029,12 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -11104,12 +11104,12 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -11179,12 +11179,12 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -11254,12 +11254,12 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -11329,12 +11329,12 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -11404,12 +11404,12 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -11479,12 +11479,12 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -24739,7 +24739,7 @@
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t xml:space="preserve">311304591</t>
+          <t xml:space="preserve">311304440</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">

--- a/public/exports-from-60/19438414.xlsx
+++ b/public/exports-from-60/19438414.xlsx
@@ -5989,7 +5989,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6364,7 +6364,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -7339,7 +7339,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311123773</t>
+          <t xml:space="preserve">311123772</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311123773</t>
+          <t xml:space="preserve">311123772</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -11554,12 +11554,12 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -11629,12 +11629,12 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -11704,12 +11704,12 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -11779,12 +11779,12 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -11854,12 +11854,12 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -11929,12 +11929,12 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -12004,12 +12004,12 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -12079,12 +12079,12 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -12154,12 +12154,12 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -12229,12 +12229,12 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -12304,12 +12304,12 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -12379,12 +12379,12 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -12529,12 +12529,12 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
